--- a/testData/testdata.xlsx
+++ b/testData/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright_Python_Framework1\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EF4394-37CA-472F-BAA9-15A2B5046BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D0E161-25B3-401A-B1F9-2937EB50A86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3A0AF91E-2598-4B80-9457-011803ED1054}"/>
   </bookViews>
@@ -30,37 +30,37 @@
     <t>JobTitle</t>
   </si>
   <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>PM</t>
-  </si>
-  <si>
-    <t>Test Lead</t>
-  </si>
-  <si>
     <t>TL</t>
   </si>
   <si>
-    <t>QA Team Lead</t>
-  </si>
-  <si>
-    <t>CO Founder</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>Imran Sarwar</t>
-  </si>
-  <si>
-    <t>Sabir Memon</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
     <t>note</t>
+  </si>
+  <si>
+    <t>New CEO</t>
+  </si>
+  <si>
+    <t>New PM</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>QA Manager</t>
+  </si>
+  <si>
+    <t>Test Engineer</t>
+  </si>
+  <si>
+    <t>Zeeshan</t>
+  </si>
+  <si>
+    <t>maria</t>
+  </si>
+  <si>
+    <t>Haroon</t>
   </si>
 </sst>
 </file>
@@ -427,43 +427,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
